--- a/out/MLP-mamba2_repeat_5_000007.xlsx
+++ b/out/MLP-mamba2_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.313807099391461</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.633306561630227</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002703077471979195</v>
+        <v>-0.0002677313617216423</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.116249030587515</v>
+        <v>3.086547111123376</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.23731537134621</v>
+        <v>6.177865618610708</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4672954430242903</v>
+        <v>0.4628415077070445</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.633306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.051474685874789</v>
+        <v>4.012858846030355</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5842713518844755</v>
+        <v>0.5787024835210878</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.633306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.752796224597569</v>
+        <v>4.707495876027614</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8375503747518886</v>
+        <v>0.8295672656878622</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.843955238983797</v>
+        <v>5.788254723494357</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8960126511264317</v>
+        <v>0.8874726537803361</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.798493309387696</v>
+        <v>6.733694987738245</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9495935482263633</v>
+        <v>0.9405428723556898</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.801734859914947</v>
+        <v>7.727374537648734</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4285332411754418</v>
+        <v>0.424448839486488</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.70842001830914</v>
+        <v>7.634949089611383</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2069619687154433</v>
+        <v>0.204990032546035</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.693474640478607</v>
+        <v>7.620146156559003</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09861121644286978</v>
+        <v>0.09767103467087479</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.683570687528068</v>
+        <v>7.610336629571071</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02921817876602292</v>
+        <v>0.02893924627183654</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.643289561943337</v>
+        <v>7.570439549183358</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01932673569270681</v>
+        <v>0.01914223224933968</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.652709598550957</v>
+        <v>7.57976989196166</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009889652660926765</v>
+        <v>0.009795192969653003</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.653149784392264</v>
+        <v>7.580205850553103</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005056497227150116</v>
+        <v>0.005008177444552025</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.653367240143238</v>
+        <v>7.580421205355791</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001897808681798028</v>
+        <v>0.001879643443785635</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.652102525655567</v>
+        <v>7.57916826670477</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001032032513414063</v>
+        <v>0.00102213244168696</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.652267721999036</v>
+        <v>7.579331906465048</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004940904089506303</v>
+        <v>0.0004901167591978387</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.652224009779117</v>
+        <v>7.579288532534498</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003039619068746027</v>
+        <v>0.0003010100415222976</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.652337799256565</v>
+        <v>7.57940118889069</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001566109577252159</v>
+        <v>0.0001555815885677305</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.65234692522439</v>
+        <v>7.579410179705206</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.392835733202904e-05</v>
+        <v>7.292926420124387e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.652337039791347</v>
+        <v>7.579400356113087</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.65235413002783</v>
+        <v>7.579417165959856</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>1.7146614275097e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.652344554843928</v>
+        <v>7.579407705863642</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.652336814202823</v>
+        <v>7.579399965222535</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.65233264103123</v>
+        <v>7.579395792050943</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.652326918752199</v>
+        <v>7.579390069771912</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.633306561630227</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.652321849396831</v>
+        <v>7.579385000416544</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.652317484422863</v>
+        <v>7.579380635442575</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.652318575669319</v>
+        <v>7.579381726689031</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.652317886062183</v>
+        <v>7.579381037081895</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.652317916374584</v>
+        <v>7.579381067394298</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.652317726922075</v>
+        <v>7.579380877941787</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.652317779968778</v>
+        <v>7.57938093098849</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.652317833015479</v>
+        <v>7.579380984035192</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.652317795124977</v>
+        <v>7.579380946144691</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.652317666297272</v>
+        <v>7.579380817316984</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.652317522313364</v>
+        <v>7.579380673333077</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.652317416219959</v>
+        <v>7.579380567239672</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.652317181298846</v>
+        <v>7.579380332318559</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.652317348017055</v>
+        <v>7.579380499036769</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.652317545047665</v>
+        <v>7.579380696067378</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.652317385907557</v>
+        <v>7.57938053692727</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.652317423798058</v>
+        <v>7.579380574817771</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.652317620828669</v>
+        <v>7.579380771848382</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.652317598094369</v>
+        <v>7.579380749114081</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.65231744653236</v>
+        <v>7.579380597552072</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.652317370751357</v>
+        <v>7.579380521771069</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.65231746926666</v>
+        <v>7.579380620286374</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.652317476844762</v>
+        <v>7.579380627864475</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.652317742078274</v>
+        <v>7.579380893097987</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.65231744653236</v>
+        <v>7.579380597552072</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.233306561630227</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.652317689031573</v>
+        <v>7.579380840051286</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.652317772390677</v>
+        <v>7.579380923410389</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.652317605672468</v>
+        <v>7.57938075669218</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.652317795124977</v>
+        <v>7.579380946144691</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.65231744653236</v>
+        <v>7.579380597552072</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.652317241923649</v>
+        <v>7.579380392943362</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.652317355595154</v>
+        <v>7.579380506614868</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.652317370751357</v>
+        <v>7.579380521771069</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.633306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.652317135830244</v>
+        <v>7.579380286849957</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.652317196455047</v>
+        <v>7.57938034747476</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.65231706762734</v>
+        <v>7.579380218647054</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.652317204033148</v>
+        <v>7.57938035505286</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.652317378329456</v>
+        <v>7.579380529349169</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.652317522313364</v>
+        <v>7.579380673333077</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.652317355595154</v>
+        <v>7.579380506614868</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.652317348017055</v>
+        <v>7.579380499036769</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.652317060049239</v>
+        <v>7.579380211068952</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.633306561630227</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.65231707520544</v>
+        <v>7.579380226225153</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.652317302548453</v>
+        <v>7.579380453568166</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.652317287392251</v>
+        <v>7.579380438411964</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.652317393485658</v>
+        <v>7.579380544505371</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.652317120674042</v>
+        <v>7.579380271693755</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.652317219189348</v>
+        <v>7.57938037020906</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7138070993914605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.652317370751357</v>
+        <v>7.579380521771069</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7138070993914605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.652317385907557</v>
+        <v>7.57938053692727</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.633306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.65231744653236</v>
+        <v>7.579380597552072</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.652317545047665</v>
+        <v>7.579380696067378</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.652317378329456</v>
+        <v>7.579380529349169</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.652317332860854</v>
+        <v>7.579380483880566</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.633306561630227</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.652317317704654</v>
+        <v>7.579380468724366</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.652317355595154</v>
+        <v>7.579380506614868</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7138070993914605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.652317370751357</v>
+        <v>7.579380521771069</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.313807099391461</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.652317363173256</v>
+        <v>7.579380514192969</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000007.xlsx
+++ b/out/MLP-mamba2_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002703077471979195</v>
+        <v>-0.0001619269270820077</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.116249030587515</v>
+        <v>1.866778318516233</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.23731537134621</v>
+        <v>3.736442339417751</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4672954430242903</v>
+        <v>0.2799317361407149</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.051474685874789</v>
+        <v>2.427022019904154</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5842713518844755</v>
+        <v>0.3500057540723804</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.633306561630227</v>
+        <v>1.285695927975013</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.752796224597569</v>
+        <v>2.84714624702011</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8375503747518886</v>
+        <v>0.5017314259199681</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.843955238983797</v>
+        <v>3.500801194130309</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.8960126511264317</v>
+        <v>0.5367535909412495</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.798493309387696</v>
+        <v>4.072614032960495</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9495935482263633</v>
+        <v>0.5688498809541147</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.801734859914947</v>
+        <v>4.673602296677592</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4285332411754418</v>
+        <v>0.2567113713638334</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.70842001830914</v>
+        <v>4.617702302476201</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2069619687154433</v>
+        <v>0.1239798589798288</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.693474640478607</v>
+        <v>4.608749306810326</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.09861121644286978</v>
+        <v>0.05907332458407126</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.683570687528068</v>
+        <v>4.602816352455759</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02921817876602292</v>
+        <v>0.01750301401019512</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.643289561943337</v>
+        <v>4.578686131640084</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01932673569270681</v>
+        <v>0.01157611707759369</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.652709598550957</v>
+        <v>4.584327686735921</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.009889652660926765</v>
+        <v>0.005922345627428683</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.653149784392264</v>
+        <v>4.584589373242288</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005056497227150116</v>
+        <v>0.003027066358030261</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.653367240143238</v>
+        <v>4.584717634324614</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001897808681798028</v>
+        <v>0.001134868685277577</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.652102525655567</v>
+        <v>4.583958008223407</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001032032513414063</v>
+        <v>0.0006162295008757277</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.652267721999036</v>
+        <v>4.58405496355088</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004940904089506303</v>
+        <v>0.0002938184614099315</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.652224009779117</v>
+        <v>4.584026773370282</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003039619068746027</v>
+        <v>0.0001799835620777876</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.652337799256565</v>
+        <v>4.58409297175492</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001566109577252159</v>
+        <v>9.176070080363244e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.65234692522439</v>
+        <v>4.584096447586115</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.392835733202904e-05</v>
+        <v>4.195737714690335e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.652337039791347</v>
+        <v>4.584088510750259</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.488670873274575e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.65235413002783</v>
+        <v>4.584096932194423</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.652344554843928</v>
+        <v>4.584089187084081</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.652336814202823</v>
+        <v>4.584082542699419</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.65233264103123</v>
+        <v>4.584078038796463</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.652326918752199</v>
+        <v>4.584072605664995</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.652321849396831</v>
+        <v>4.584067559043927</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.652317484422863</v>
+        <v>4.584067877324143</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.652318575669319</v>
+        <v>4.5840689685706</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.652317886062183</v>
+        <v>4.584068278963464</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.652317916374584</v>
+        <v>4.584068309275867</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.652317726922075</v>
+        <v>4.584068119823356</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.652317779968778</v>
+        <v>4.58406817287006</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.652317833015479</v>
+        <v>4.584068225916762</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.652317795124977</v>
+        <v>4.58406818802626</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.652317666297272</v>
+        <v>4.584068059198553</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.652317522313364</v>
+        <v>4.584067915214646</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.652317416219959</v>
+        <v>4.58406780912124</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.652317181298846</v>
+        <v>4.584067574200128</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.652317348017055</v>
+        <v>4.584067740918337</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.652317545047665</v>
+        <v>4.584067937948947</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.652317385907557</v>
+        <v>4.584067778808839</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.652317423798058</v>
+        <v>4.58406781669934</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.652317620828669</v>
+        <v>4.584068013729951</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.652317598094369</v>
+        <v>4.584067990995649</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.65231744653236</v>
+        <v>4.584067839433641</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.652317370751357</v>
+        <v>4.584067763652637</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.65231746926666</v>
+        <v>4.584067862167943</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.652317476844762</v>
+        <v>4.584067869746043</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.652317742078274</v>
+        <v>4.584068134979558</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.65231744653236</v>
+        <v>4.584067839433641</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.652317689031573</v>
+        <v>4.584068081932854</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.652317772390677</v>
+        <v>4.584068165291958</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.652317605672468</v>
+        <v>4.58406799857375</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.652317795124977</v>
+        <v>4.58406818802626</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.65231744653236</v>
+        <v>4.584067839433641</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.652317241923649</v>
+        <v>4.584067634824931</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.652317355595154</v>
+        <v>4.584067748496437</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.652317370751357</v>
+        <v>4.584067763652637</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.652317135830244</v>
+        <v>4.584067528731526</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.652317196455047</v>
+        <v>4.584067589356328</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.65231706762734</v>
+        <v>4.584067460528622</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.652317204033148</v>
+        <v>4.584067596934429</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.652317378329456</v>
+        <v>4.584067771230738</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.652317522313364</v>
+        <v>4.584067915214646</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.652317355595154</v>
+        <v>4.584067748496437</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.652317348017055</v>
+        <v>4.584067740918337</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.652317060049239</v>
+        <v>4.584067452950522</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.65231707520544</v>
+        <v>4.584067468106722</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.652317302548453</v>
+        <v>4.584067695449734</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.652317287392251</v>
+        <v>4.584067680293533</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.652317393485658</v>
+        <v>4.584067786386939</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.652317120674042</v>
+        <v>4.584067513575325</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.652317219189348</v>
+        <v>4.58406761209063</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.652317370751357</v>
+        <v>4.584067763652637</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.652317385907557</v>
+        <v>4.584067778808839</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.633306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.65231744653236</v>
+        <v>4.584067839433641</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.652317545047665</v>
+        <v>4.584067937948947</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.652317378329456</v>
+        <v>4.584067771230738</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.652317332860854</v>
+        <v>4.584067725762135</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.652317317704654</v>
+        <v>4.584067710605935</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.652317355595154</v>
+        <v>4.584067748496437</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.652317370751357</v>
+        <v>4.584067763652637</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.652317363173256</v>
+        <v>4.584067756074537</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000007.xlsx
+++ b/out/MLP-mamba2_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3068611025810242</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4998860657215118</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.44283127784729</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.213549330830574</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4495380222797394</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.3614224791526794</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3479496836662292</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2203729003667831</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4753285646438599</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3143278360366821</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.325473427772522</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3216468989849091</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5361822843551636</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2185860276222229</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.1966242641210556</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2929066717624664</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4579071402549744</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.2754801213741302</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.32790806889534</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.663321316242218</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.7289054393768311</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.8129253387451172</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3532013297080994</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4386453330516815</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4413423538208008</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3552589118480682</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3229766488075256</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.7610694766044617</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3555459678173065</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4507804811000824</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4024638533592224</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2165157496929169</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5048239827156067</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5475901365280151</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.485695927975013</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.8157863616943359</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.485695927975013</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.9354895949363708</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.485695927975013</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.590008556842804</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.485695927975013</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.7277414202690125</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.812069948312913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001619269270820077</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.866778318516233</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.3108668029308319</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.736442339417751</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2799317361407149</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.6132227778434753</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.427022019904154</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3500057540723804</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6614334583282471</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.285695927975013</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.84714624702011</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5017314259199681</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8776411414146423</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.485695927975013</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.500801194130309</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5367535909412495</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.904941737651825</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.485695927975013</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.072614032960495</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5688498809541147</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7525664567947388</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.485695927975013</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.673602296677592</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2567113713638334</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5406814217567444</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.617702302476201</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1239798589798288</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.09650982916355133</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.608749306810326</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05907332458407126</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.09222689270973206</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.602816352455759</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01750301401019512</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3992289304733276</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.578686131640084</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01157611707759369</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4253223538398743</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.584327686735921</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005922345627428683</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.1594919264316559</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.584589373242288</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003027066358030261</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3175831437110901</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.584717634324614</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001134868685277577</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5020858645439148</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.583958008223407</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006162295008757277</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4742320477962494</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.58405496355088</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002938184614099315</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6978711485862732</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.584026773370282</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001799835620777876</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5891575813293457</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.58409297175492</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.176070080363244e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2608171701431274</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.584096447586115</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.195737714690335e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9471580982208252</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.584088510750259</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.569951306630508e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3183842897415161</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.584096932194423</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.987335331640211e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.1150970086455345</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.584089187084081</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.176214944912711e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3706764280796051</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.584082542699419</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.1989686638116837</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.584078038796463</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.343229204416275</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.584072605664995</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.8473080992698669</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6120699483129129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.584067559043927</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9220814108848572</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.584067877324143</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8593990802764893</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.5840689685706</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.09834824502468109</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.584068278963464</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.02744960971176624</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.584068309275867</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.09183167666196823</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.584068119823356</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.2165275514125824</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.58406817287006</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1542022675275803</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.584068225916762</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2104882746934891</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.58406818802626</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2186290621757507</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.584068059198553</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2726658284664154</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.584067915214646</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4321785569190979</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3807167708873749</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.58406780912124</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3979080319404602</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.1948980689048767</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.8119490742683411</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.584067574200128</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.7653793096542358</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.584067740918337</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.1664934307336807</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.584067937948947</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4137618541717529</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.584067778808839</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7059590816497803</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.58406781669934</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.565795361995697</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.584068013729951</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2319444864988327</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.584067990995649</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3084046244621277</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.584067839433641</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.5140306949615479</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.584067763652637</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4523771107196808</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.584067862167943</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.7142820954322815</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.584067869746043</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3206352293491364</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.812069948312913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.584068134979558</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5917333364486694</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.584067839433641</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.6442537903785706</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.584068081932854</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1397445797920227</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.584068165291958</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.8115767240524292</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.58406799857375</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.1273356974124908</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.58406818802626</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.1998911947011948</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.584067839433641</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2958724498748779</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.584067634824931</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4142890870571136</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.584067748496437</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1669989973306656</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.584067763652637</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5153087377548218</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.584067528731526</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.1830170303583145</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.584067589356328</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6189049482345581</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.584067460528622</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.8871644139289856</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.584067596934429</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5656381249427795</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.584067771230738</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2101472616195679</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.584067915214646</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4655434191226959</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.584067748496437</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.09120385348796844</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.584067740918337</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3661769330501556</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.584067452950522</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.7614662647247314</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.584067468106722</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3733389973640442</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.584067695449734</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.730596661567688</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.584067680293533</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.09457049518823624</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.584067786386939</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.452146053314209</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.584067513575325</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6992330551147461</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.58406761209063</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.474413275718689</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.584067763652637</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4945281744003296</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.584067778808839</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.5209464430809021</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.812069948312913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.5800701379776001</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.584067839433641</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3092789947986603</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.584067937948947</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2455567121505737</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.584067771230738</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4072525799274445</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3568356931209564</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.584067725762135</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.508820116519928</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.584067710605935</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4372771680355072</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.584067748496437</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4406777620315552</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.584067763652637</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4398178160190582</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.8600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.584067756074537</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_5_000007.xlsx
+++ b/out/MLP-mamba2_repeat_5_000007.xlsx
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.213549330830574</v>
+        <v>0.2135493457317352</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3479496836662292</v>
+        <v>0.3479497134685516</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.2203729003667831</v>
+        <v>0.2203728705644608</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.325473427772522</v>
+        <v>0.3254734575748444</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.8129253387451172</v>
+        <v>0.8129252195358276</v>
       </c>
       <c r="JB23" t="n">
         <v>0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4386453330516815</v>
+        <v>0.4386453926563263</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4507804811000824</v>
+        <v>0.4507804214954376</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4024638533592224</v>
+        <v>0.4024638831615448</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2165157496929169</v>
+        <v>0.2165157645940781</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.5048239827156067</v>
+        <v>0.5048240423202515</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.7525664567947388</v>
+        <v>0.7525665760040283</v>
       </c>
       <c r="JB45" t="n">
         <v>0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.09650982916355133</v>
+        <v>0.09650980681180954</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.09222689270973206</v>
+        <v>0.09222692251205444</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4253223538398743</v>
+        <v>0.4253223836421967</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.3183842897415161</v>
+        <v>0.3183842599391937</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.1199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3706764280796051</v>
+        <v>0.3706763684749603</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.1989686638116837</v>
+        <v>0.1989686787128448</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.09183167666196823</v>
+        <v>0.09183171391487122</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.2165275514125824</v>
+        <v>0.216527596116066</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1542022675275803</v>
+        <v>0.1542022824287415</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2104882746934891</v>
+        <v>0.2104883193969727</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2186290621757507</v>
+        <v>0.2186290770769119</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.2726658284664154</v>
+        <v>0.2726657390594482</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.7653793096542358</v>
+        <v>0.7653794884681702</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1397445797920227</v>
+        <v>0.1397446095943451</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.1273356974124908</v>
+        <v>0.1273356676101685</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.1998911947011948</v>
+        <v>0.199891209602356</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1669989973306656</v>
+        <v>0.166999027132988</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.8871644139289856</v>
+        <v>0.8871643543243408</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2101472616195679</v>
+        <v>0.2101472765207291</v>
       </c>
       <c r="JB105" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.7614662647247314</v>
+        <v>0.7614662051200867</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3733389973640442</v>
+        <v>0.3733389377593994</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.09457049518823624</v>
+        <v>0.09457050263881683</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.474413275718689</v>
+        <v>0.4744132459163666</v>
       </c>
       <c r="JB115" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.3092789947986603</v>
+        <v>0.3092790246009827</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2455567121505737</v>
+        <v>0.2455567419528961</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3568356931209564</v>
+        <v>0.3568356335163116</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4398178160190582</v>
+        <v>0.4398177564144135</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8600000000000003</v>
